--- a/site/StructureDefinition-uy-org-identifier.xlsx
+++ b/site/StructureDefinition-uy-org-identifier.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="157">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T01:23:13-03:00</t>
+    <t>2026-10-28T18:02:56-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -277,7 +277,10 @@
 </t>
   </si>
   <si>
-    <t>ID lógico de este artefacto.</t>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -287,13 +290,23 @@
   </si>
   <si>
     <t>Identifier.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Contenido adicional definido por implementaciones.</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -323,10 +336,13 @@
 </t>
   </si>
   <si>
-    <t>El propósito o estatus de este identificador.</t>
-  </si>
-  <si>
-    <t>Las aplicaciones pueden considerar permanente un identificador salvo que se indique explícitamente que es temporal.</t>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
   </si>
   <si>
     <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
@@ -335,7 +351,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>Propósito de uso del identificador.</t>
+    <t>Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -354,7 +370,10 @@
 </t>
   </si>
   <si>
-    <t>Codificación del tipo de identificador.</t>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
@@ -375,217 +394,29 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>Categoría del identificador, utilizada para elegirlo según el propósito.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>CX.5</t>
   </si>
   <si>
-    <t>Identifier.type.id</t>
-  </si>
-  <si>
-    <t>Identificador del elemento.</t>
-  </si>
-  <si>
-    <t>Identificador del elemento para referencias internas dentro del recurso.</t>
-  </si>
-  <si>
-    <t>Identifier.type.extension</t>
-  </si>
-  <si>
-    <t>Extensiones del elemento.</t>
-  </si>
-  <si>
-    <t>Información adicional definida mediante extensiones.</t>
-  </si>
-  <si>
-    <t>Identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Codificación del concepto.</t>
-  </si>
-  <si>
-    <t>Representación del concepto mediante un código de un sistema terminológico.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>Identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Identifier.type.coding.system</t>
+    <t>Identifier.system</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
-    <t>Sistema de codificación.</t>
-  </si>
-  <si>
-    <t>URI que identifica el sistema terminológico que define el código.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Identifier.type.coding.version</t>
-  </si>
-  <si>
-    <t>Versión del sistema de codificación.</t>
-  </si>
-  <si>
-    <t>Versión del sistema terminológico utilizada para interpretar el código.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Identifier.type.coding.code</t>
-  </si>
-  <si>
-    <t>Código del concepto.</t>
-  </si>
-  <si>
-    <t>Símbolo definido por el sistema terminológico.</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Identifier.type.coding.display</t>
-  </si>
-  <si>
-    <t>Texto asociado al código.</t>
-  </si>
-  <si>
-    <t>Representación legible del código definida por el sistema terminológico.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Identifier.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Código seleccionado por el usuario.</t>
-  </si>
-  <si>
-    <t>Indica si el usuario seleccionó directamente esta codificación.</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Identifier.type.text</t>
-  </si>
-  <si>
-    <t>Representación textual del concepto.</t>
-  </si>
-  <si>
-    <t>Texto que expresa el significado del concepto.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>Namespace/URI que define de manera unívoca el sistema emisor del identificador.</t>
-  </si>
-  <si>
-    <t>Identifier.system distingue siempre entre mayúsculas y minúsculas.</t>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
   </si>
   <si>
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
@@ -606,7 +437,10 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>El valor alfanumérico o numérico único del identificador.</t>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
     <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
@@ -631,7 +465,10 @@
 </t>
   </si>
   <si>
-    <t>Periodo de validez del identificador.</t>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>CX.7 + CX.8</t>
@@ -650,10 +487,13 @@
 </t>
   </si>
   <si>
-    <t>Organización que emite, administra o es responsable del identificador.</t>
-  </si>
-  <si>
-    <t>La organización emisora puede representarse únicamente mediante display, sin incluir reference.</t>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
@@ -964,13 +804,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM21"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="29.03125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="29.03125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.63671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="16.63671875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="6.890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="11.10546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
@@ -981,7 +821,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="198.73046875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="145.7421875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -991,14 +831,14 @@
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="56.1875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="39.81640625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="85.70703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="40.59765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="20.92578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.8984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1269,7 +1109,7 @@
         <v>86</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1320,7 +1160,7 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>76</v>
@@ -1338,7 +1178,7 @@
         <v>20</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AM3" t="s" s="2">
         <v>20</v>
@@ -1346,14 +1186,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
@@ -1372,15 +1212,17 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N4" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="N4" t="s" s="2">
+        <v>95</v>
+      </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>20</v>
@@ -1417,19 +1259,19 @@
         <v>20</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>76</v>
@@ -1441,13 +1283,13 @@
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>20</v>
@@ -1455,10 +1297,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1475,25 +1317,25 @@
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="O5" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="P5" t="s" s="2">
         <v>20</v>
@@ -1518,13 +1360,13 @@
         <v>20</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>20</v>
@@ -1542,7 +1384,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -1557,10 +1399,10 @@
         <v>80</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>20</v>
@@ -1568,10 +1410,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1591,22 +1433,22 @@
         <v>20</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="O6" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="P6" t="s" s="2">
         <v>20</v>
@@ -1616,46 +1458,46 @@
         <v>20</v>
       </c>
       <c r="S6" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="T6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X6" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="T6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X6" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -1670,10 +1512,10 @@
         <v>80</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>20</v>
@@ -1681,10 +1523,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1692,7 +1534,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>84</v>
@@ -1704,19 +1546,23 @@
         <v>20</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="N7" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="O7" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="P7" t="s" s="2">
         <v>20</v>
       </c>
@@ -1728,7 +1574,7 @@
         <v>20</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="U7" t="s" s="2">
         <v>20</v>
@@ -1764,7 +1610,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -1776,24 +1622,24 @@
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>20</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1801,10 +1647,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1813,18 +1659,20 @@
         <v>20</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N8" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>20</v>
@@ -1837,7 +1685,7 @@
         <v>20</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="U8" t="s" s="2">
         <v>20</v>
@@ -1861,48 +1709,48 @@
         <v>20</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1913,7 +1761,7 @@
         <v>76</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -1922,23 +1770,19 @@
         <v>20</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="O9" t="s" s="2">
-        <v>129</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>20</v>
       </c>
@@ -1986,13 +1830,13 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
@@ -2001,21 +1845,21 @@
         <v>80</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2035,18 +1879,20 @@
         <v>20</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>20</v>
@@ -2095,7 +1941,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2107,1241 +1953,16 @@
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>20</v>
+        <v>154</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K11" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="P12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K13" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="O13" s="2"/>
-      <c r="P13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K14" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="P14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK14" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="P15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="P16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="P17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q17" s="2"/>
-      <c r="R17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="G18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K18" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="P18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q18" s="2"/>
-      <c r="R18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T18" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="G19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K19" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O19" s="2"/>
-      <c r="P19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q19" s="2"/>
-      <c r="R19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K20" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q20" s="2"/>
-      <c r="R20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K21" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O21" s="2"/>
-      <c r="P21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q21" s="2"/>
-      <c r="R21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
   </sheetData>
